--- a/tams-invest-parent/tams-invest-settle/src/main/resources/tpl/DvpOrdersManagement001Dvp.xlsx
+++ b/tams-invest-parent/tams-invest-settle/src/main/resources/tpl/DvpOrdersManagement001Dvp.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>业务编号</t>
   </si>
@@ -85,13 +85,16 @@
       <t>支付系统号</t>
     </r>
   </si>
+  <si>
+    <t>登记托管机构</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -148,7 +151,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -518,14 +521,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="11" max="11" width="25.77734375" customWidth="1"/>
-    <col min="14" max="14" width="20.44140625" style="1" customWidth="1"/>
+    <col min="14" max="15" width="20.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -568,7 +571,10 @@
       <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" t="s">
         <v>9</v>
       </c>
     </row>
